--- a/DataTables/DetailText/剧情/000_06金钱过低.xlsx
+++ b/DataTables/DetailText/剧情/000_06金钱过低.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0284769-0934-43B1-A219-CF24ACBD3218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114E5171-1CA9-4E7E-BDA9-95F81C56381F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -179,6 +166,21 @@
   </si>
   <si>
     <t>因经营不善，医馆被迫关闭</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>000_06</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>gameover</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>东璧啊，咱们这医馆已经经营不下去了，我们收拾行李回乡下老家吧…</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -203,7 +205,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>/0</t>
+      <t>/000_</t>
     </r>
     <r>
       <rPr>
@@ -225,21 +227,6 @@
       </rPr>
       <t>1.png</t>
     </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>000_06</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>gameover</t>
-  </si>
-  <si>
-    <t>Music</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>东璧啊，咱们这医馆已经经营不下去了，我们收拾行李回乡下老家吧…</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -485,7 +472,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -696,7 +683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.625" customWidth="1"/>
@@ -714,7 +701,7 @@
     <col min="19" max="20" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
@@ -776,9 +763,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>31</v>
@@ -799,7 +786,7 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
@@ -1089,7 +1076,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1111,7 +1098,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I2" s="28"/>
     </row>
@@ -1127,7 +1114,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="30" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>36</v>
